--- a/CapstoneSheet.xlsx
+++ b/CapstoneSheet.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Grant\Desktop\Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130B0F5F-AF9B-417C-AD4C-A5FFFDB99C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10905EAD-576E-4DF0-9808-EF1D4A31E31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{40F1218A-A2E3-4851-AB53-6F5687E18533}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="3" xr2:uid="{40F1218A-A2E3-4851-AB53-6F5687E18533}"/>
   </bookViews>
   <sheets>
     <sheet name="Pool1" sheetId="3" r:id="rId1"/>
     <sheet name="Pool2" sheetId="2" r:id="rId2"/>
+    <sheet name="Pool3" sheetId="4" r:id="rId3"/>
+    <sheet name="Bracket" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,22 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
-  <si>
-    <t xml:space="preserve">Teams </t>
-  </si>
-  <si>
-    <t>Wins</t>
-  </si>
-  <si>
-    <t>Loss</t>
-  </si>
-  <si>
-    <t>Tie</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="46">
   <si>
     <t>Mexico</t>
   </si>
@@ -60,41 +47,155 @@
     <t>Canada</t>
   </si>
   <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>team</t>
+  </si>
+  <si>
+    <t>pts</t>
+  </si>
+  <si>
+    <t>gd</t>
+  </si>
+  <si>
+    <t>gf</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>Czechia</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Scotland</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>Bosnia</t>
+  </si>
+  <si>
+    <t>Curacoa</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Uzbekistan</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Turkiye</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
     <t>England</t>
   </si>
   <si>
-    <t>Brazil</t>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Uraguay</t>
   </si>
   <si>
     <t>Argentina</t>
   </si>
   <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Draw</t>
-  </si>
-  <si>
-    <t>Win</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>Germany</t>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>DR Congo</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>Iran</t>
+  </si>
+  <si>
+    <t>ga</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,8 +218,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A969E0A-C8B4-43EE-8F98-8EFD557747FB}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" customWidth="1"/>
@@ -463,74 +565,119 @@
     <col min="5" max="5" width="28.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D3" s="1">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1">
+        <v>6</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <v>10</v>
-      </c>
-      <c r="C3">
+      <c r="D5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
         <v>0</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -540,105 +687,489 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B27E990-71D1-419C-A7A0-63ED808646EC}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1">
+        <v>4</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1">
+        <v>-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65BC2611-D7E8-46E0-BDE0-9EB7D139E41F}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1">
+        <v>-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A2075B-4276-4445-A8CD-4EDF7B738191}">
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="N1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="N19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>17</v>
-      </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-      <c r="C4">
+      <c r="N22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>10</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
+      <c r="N23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="C25" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" t="s">
         <v>20</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
